--- a/data/trans_dic/P1412-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1412-Edad-trans_dic.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -913,32 +913,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,41</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,4</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,42</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,55</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,63</t>
+          <t>0,28; 1,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,76</t>
+          <t>0,08; 0,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,03</t>
+          <t>0,26; 1,25</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,43</t>
+          <t>0,87; 3,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,92</t>
+          <t>0,28; 1,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,15</t>
+          <t>0,23; 2,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,13</t>
+          <t>0,23; 1,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,68</t>
+          <t>0,45; 1,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,38</t>
+          <t>0,23; 1,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,18</t>
+          <t>0,66; 2,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,41</t>
+          <t>0,5; 1,42</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,13</t>
+          <t>1,14; 5,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,74</t>
+          <t>0,92; 4,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,01</t>
+          <t>1,33; 3,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,55</t>
+          <t>0,28; 2,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,99</t>
+          <t>0,53; 3,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,49</t>
+          <t>0,53; 2,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,29</t>
+          <t>0,9; 3,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,18</t>
+          <t>1,02; 3,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,13</t>
+          <t>1,11; 2,5</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,43</t>
+          <t>2,16; 7,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,1</t>
+          <t>1,28; 5,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,92</t>
+          <t>2,33; 5,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,85</t>
+          <t>2,26; 6,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,1</t>
+          <t>0,63; 3,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,33</t>
+          <t>0,89; 2,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,81</t>
+          <t>2,57; 5,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,76</t>
+          <t>1,27; 3,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,22</t>
+          <t>1,66; 3,37</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,02</t>
+          <t>0,41; 1,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,1</t>
+          <t>0,5; 1,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,23</t>
+          <t>0,68; 1,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,04</t>
+          <t>0,45; 1,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,85</t>
+          <t>0,31; 0,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,69</t>
+          <t>0,39; 0,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,93</t>
+          <t>0,52; 0,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,87</t>
+          <t>0,45; 0,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,85</t>
+          <t>0,59; 0,93</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4970</t>
+          <t>0; 5010</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7870</t>
+          <t>0; 7144</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4974</t>
+          <t>0; 4001</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6827</t>
+          <t>0; 7083</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5134</t>
+          <t>0; 4967</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 8591</t>
+          <t>0; 7513</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5979</t>
+          <t>0; 5177</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 8081</t>
+          <t>0; 7139</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>787</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1928</t>
         </is>
       </c>
     </row>
@@ -2086,37 +2086,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5266</t>
+          <t>0; 6092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5556</t>
+          <t>0; 6924</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4718</t>
+          <t>0; 6354</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3647</t>
+          <t>0; 3166</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5623</t>
+          <t>0; 5663</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5630</t>
+          <t>0; 5380</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5874</t>
+          <t>0; 7570</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7769</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7830</t>
+          <t>0; 6622</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1411; 14495</t>
+          <t>1994; 12960</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>608; 5395</t>
+          <t>611; 5941</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6432</t>
+          <t>0; 6906</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3090; 16540</t>
+          <t>3740; 17971</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>10621</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5115</t>
+          <t>0; 4654</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4232; 16412</t>
+          <t>4168; 15940</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1703; 10769</t>
+          <t>1728; 10320</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1044; 9626</t>
+          <t>1033; 9292</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1161; 10581</t>
+          <t>1159; 9532</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2377; 9131</t>
+          <t>2760; 10989</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1985; 12123</t>
+          <t>1977; 11308</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6613; 21229</t>
+          <t>6413; 20558</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5027; 15626</t>
+          <t>6081; 17299</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>14475</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3254; 19001</t>
+          <t>3532; 16936</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3832; 15836</t>
+          <t>3075; 15673</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5184; 14716</t>
+          <t>5416; 15920</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>974; 9029</t>
+          <t>977; 7938</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1997; 11305</t>
+          <t>2017; 11715</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1220; 9065</t>
+          <t>2344; 8955</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5950; 21837</t>
+          <t>5994; 21067</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6906; 22633</t>
+          <t>7282; 22034</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6054; 20808</t>
+          <t>9373; 21165</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>18850</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5116; 18558</t>
+          <t>5403; 17924</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3280; 13113</t>
+          <t>3297; 13164</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6118; 16751</t>
+          <t>7227; 18487</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8933; 26572</t>
+          <t>8776; 26177</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3635; 16390</t>
+          <t>2530; 15038</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3307; 9892</t>
+          <t>4117; 11455</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17301; 37041</t>
+          <t>16362; 38128</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8146; 24682</t>
+          <t>8343; 24063</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11345; 22780</t>
+          <t>12870; 26122</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>53643</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14015; 34907</t>
+          <t>14192; 34240</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16843; 37325</t>
+          <t>16958; 38075</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21197; 42526</t>
+          <t>23976; 45421</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16104; 37053</t>
+          <t>16087; 36747</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10542; 30233</t>
+          <t>11125; 30679</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12410; 25356</t>
+          <t>14728; 28149</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34978; 64582</t>
+          <t>35976; 65540</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33386; 60484</t>
+          <t>31245; 59836</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36207; 60708</t>
+          <t>42561; 67365</t>
         </is>
       </c>
     </row>
